--- a/TerytLoad/AppData/Dictionaries/TerytUlicPoprawki_braki.xlsx
+++ b/TerytLoad/AppData/Dictionaries/TerytUlicPoprawki_braki.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TerytUlicPoprawki" sheetId="1" r:id="Rd78774c2552f41eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TerytUlicPoprawki" sheetId="1" r:id="Rfa8cc363da6d4b88"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/TerytLoad/AppData/Dictionaries/TerytUlicPoprawki_braki.xlsx
+++ b/TerytLoad/AppData/Dictionaries/TerytUlicPoprawki_braki.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TerytUlicPoprawki" sheetId="1" r:id="Rfa8cc363da6d4b88"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TerytUlicPoprawki" sheetId="1" r:id="Rfcb30b8180fd42f6"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/TerytLoad/AppData/Dictionaries/TerytUlicPoprawki_braki.xlsx
+++ b/TerytLoad/AppData/Dictionaries/TerytUlicPoprawki_braki.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TerytUlicPoprawki" sheetId="1" r:id="Rfcb30b8180fd42f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TerytUlicPoprawki" sheetId="1" r:id="Ra1cc047f9e7c4321"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/TerytLoad/AppData/Dictionaries/TerytUlicPoprawki_braki.xlsx
+++ b/TerytLoad/AppData/Dictionaries/TerytUlicPoprawki_braki.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TerytUlicPoprawki" sheetId="1" r:id="Ra1cc047f9e7c4321"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TerytUlicPoprawki" sheetId="1" r:id="R0cea7a65ec4342ef"/>
   </x:sheets>
 </x:workbook>
 </file>
